--- a/Jadwal Kuliah 20261_Prodi Sains Data.xlsx
+++ b/Jadwal Kuliah 20261_Prodi Sains Data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive - ITPLN\Desktop\Dokumen PDSI\SRS Sistem Informasi\BAA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\siperkul\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D8EBE3B4-4230-4E1A-A866-78F9E0DE1D81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1F9D783-599E-49A5-954C-5252F1BF0BA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{B11C22F0-6B64-4B1B-BD49-41A1A49AA758}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B11C22F0-6B64-4B1B-BD49-41A1A49AA758}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="107">
   <si>
     <t>No</t>
   </si>
@@ -292,13 +292,70 @@
   </si>
   <si>
     <t>Kurikulum</t>
+  </si>
+  <si>
+    <t>Kelas 102 (Indonesia Power)</t>
+  </si>
+  <si>
+    <t>Kelas 111 (PLN Gas dan Geotermal)</t>
+  </si>
+  <si>
+    <t>Kelas 109 (Enjiniiring)</t>
+  </si>
+  <si>
+    <t>Kelas 106 (PLN Tarakan)</t>
+  </si>
+  <si>
+    <t>Kelas 101 (Indonesia Power)</t>
+  </si>
+  <si>
+    <t>Ruang Kuliah 603</t>
+  </si>
+  <si>
+    <t>Ruang Kuliah 602</t>
+  </si>
+  <si>
+    <t>Ruang Kuliah 607</t>
+  </si>
+  <si>
+    <t>Ruang Kuliah 308</t>
+  </si>
+  <si>
+    <t>Ruang Kuliah 709</t>
+  </si>
+  <si>
+    <t>Ruang Kuliah 710</t>
+  </si>
+  <si>
+    <t>Ruang Kuliah 411</t>
+  </si>
+  <si>
+    <t>Ruang Kuliah 410</t>
+  </si>
+  <si>
+    <t>Ruang Kuliah 407</t>
+  </si>
+  <si>
+    <t>Ruang Ujian 911</t>
+  </si>
+  <si>
+    <t>Ruang Ujian 910</t>
+  </si>
+  <si>
+    <t>Ruang Ujian 908</t>
+  </si>
+  <si>
+    <t>Ruang Ujian 909</t>
+  </si>
+  <si>
+    <t>Ruang Ujian 907</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -327,8 +384,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF212529"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -377,8 +440,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -414,11 +483,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFDEE2E6"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FFDEE2E6"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFDEE2E6"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -479,11 +561,15 @@
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -839,21 +925,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="27" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
-      <c r="K1" s="26"/>
-      <c r="L1" s="26"/>
-      <c r="M1" s="26"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
+      <c r="K1" s="27"/>
+      <c r="L1" s="27"/>
+      <c r="M1" s="27"/>
     </row>
     <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -893,11 +979,11 @@
       <c r="L3" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="M3" s="27" t="s">
+      <c r="M3" s="26" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="17" t="s">
         <v>63</v>
       </c>
@@ -932,9 +1018,11 @@
       <c r="L4" s="22">
         <v>2025</v>
       </c>
-      <c r="M4" s="2"/>
-    </row>
-    <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M4" s="28" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="17" t="s">
         <v>64</v>
       </c>
@@ -969,9 +1057,11 @@
       <c r="L5" s="22">
         <v>2025</v>
       </c>
-      <c r="M5" s="2"/>
-    </row>
-    <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M5" s="28" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="9" t="s">
         <v>65</v>
       </c>
@@ -1006,9 +1096,11 @@
       <c r="L6" s="22">
         <v>2025</v>
       </c>
-      <c r="M6" s="2"/>
-    </row>
-    <row r="7" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M6" s="28" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="9" t="s">
         <v>66</v>
       </c>
@@ -1045,9 +1137,11 @@
       <c r="L7" s="22">
         <v>2025</v>
       </c>
-      <c r="M7" s="2"/>
-    </row>
-    <row r="8" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M7" s="29" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="9" t="s">
         <v>67</v>
       </c>
@@ -1084,9 +1178,11 @@
       <c r="L8" s="22">
         <v>2025</v>
       </c>
-      <c r="M8" s="2"/>
-    </row>
-    <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M8" s="29" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
         <v>68</v>
       </c>
@@ -1123,9 +1219,11 @@
       <c r="L9" s="22">
         <v>2025</v>
       </c>
-      <c r="M9" s="2"/>
-    </row>
-    <row r="10" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M9" s="28" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
         <v>69</v>
       </c>
@@ -1160,9 +1258,11 @@
       <c r="L10" s="22">
         <v>2025</v>
       </c>
-      <c r="M10" s="2"/>
-    </row>
-    <row r="11" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M10" s="28" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="17" t="s">
         <v>70</v>
       </c>
@@ -1197,9 +1297,11 @@
       <c r="L11" s="22">
         <v>2025</v>
       </c>
-      <c r="M11" s="2"/>
-    </row>
-    <row r="12" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M11" s="28" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="17" t="s">
         <v>71</v>
       </c>
@@ -1236,9 +1338,11 @@
       <c r="L12" s="22">
         <v>2025</v>
       </c>
-      <c r="M12" s="2"/>
-    </row>
-    <row r="13" spans="1:13" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="M12" s="28" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="31.8" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
         <v>72</v>
       </c>
@@ -1271,9 +1375,11 @@
       <c r="L13" s="22">
         <v>2025</v>
       </c>
-      <c r="M13" s="2"/>
-    </row>
-    <row r="14" spans="1:13" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="M13" s="28" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="31.8" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
         <v>73</v>
       </c>
@@ -1306,9 +1412,11 @@
       <c r="L14" s="22">
         <v>2025</v>
       </c>
-      <c r="M14" s="2"/>
-    </row>
-    <row r="15" spans="1:13" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="M14" s="28" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="31.8" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
         <v>74</v>
       </c>
@@ -1341,9 +1449,11 @@
       <c r="L15" s="22">
         <v>2025</v>
       </c>
-      <c r="M15" s="2"/>
-    </row>
-    <row r="16" spans="1:13" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="M15" s="28" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="31.8" x14ac:dyDescent="0.35">
       <c r="A16" s="17" t="s">
         <v>75</v>
       </c>
@@ -1378,9 +1488,11 @@
       <c r="L16" s="22">
         <v>2025</v>
       </c>
-      <c r="M16" s="2"/>
-    </row>
-    <row r="17" spans="1:13" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="M16" s="28" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="31.8" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
         <v>76</v>
       </c>
@@ -1415,9 +1527,11 @@
       <c r="L17" s="22">
         <v>2025</v>
       </c>
-      <c r="M17" s="2"/>
-    </row>
-    <row r="18" spans="1:13" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="M17" s="28" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="32.4" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A18" s="4" t="s">
         <v>77</v>
       </c>
@@ -1454,9 +1568,11 @@
       <c r="L18" s="22">
         <v>2025</v>
       </c>
-      <c r="M18" s="2"/>
-    </row>
-    <row r="19" spans="1:13" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="M18" s="28" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
         <v>78</v>
       </c>
@@ -1491,9 +1607,11 @@
       <c r="L19" s="22">
         <v>2025</v>
       </c>
-      <c r="M19" s="2"/>
-    </row>
-    <row r="20" spans="1:13" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="M19" s="29" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="s">
         <v>79</v>
       </c>
@@ -1530,9 +1648,11 @@
       <c r="L20" s="22">
         <v>2025</v>
       </c>
-      <c r="M20" s="2"/>
-    </row>
-    <row r="21" spans="1:13" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="M20" s="29" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
         <v>80</v>
       </c>
@@ -1569,9 +1689,11 @@
       <c r="L21" s="22">
         <v>2025</v>
       </c>
-      <c r="M21" s="2"/>
-    </row>
-    <row r="22" spans="1:13" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="M21" s="29" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="s">
         <v>81</v>
       </c>
@@ -1608,7 +1730,9 @@
       <c r="L22" s="22">
         <v>2025</v>
       </c>
-      <c r="M22" s="2"/>
+      <c r="M22" s="29" t="s">
+        <v>106</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="E1:E22" xr:uid="{95B44815-789E-44D5-B165-88C51CD1CA07}"/>

--- a/Jadwal Kuliah 20261_Prodi Sains Data.xlsx
+++ b/Jadwal Kuliah 20261_Prodi Sains Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\siperkul\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1F9D783-599E-49A5-954C-5252F1BF0BA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{689E7AC7-2FB6-44C3-AB99-613FB0242F0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B11C22F0-6B64-4B1B-BD49-41A1A49AA758}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="88">
   <si>
     <t>No</t>
   </si>
@@ -292,63 +292,6 @@
   </si>
   <si>
     <t>Kurikulum</t>
-  </si>
-  <si>
-    <t>Kelas 102 (Indonesia Power)</t>
-  </si>
-  <si>
-    <t>Kelas 111 (PLN Gas dan Geotermal)</t>
-  </si>
-  <si>
-    <t>Kelas 109 (Enjiniiring)</t>
-  </si>
-  <si>
-    <t>Kelas 106 (PLN Tarakan)</t>
-  </si>
-  <si>
-    <t>Kelas 101 (Indonesia Power)</t>
-  </si>
-  <si>
-    <t>Ruang Kuliah 603</t>
-  </si>
-  <si>
-    <t>Ruang Kuliah 602</t>
-  </si>
-  <si>
-    <t>Ruang Kuliah 607</t>
-  </si>
-  <si>
-    <t>Ruang Kuliah 308</t>
-  </si>
-  <si>
-    <t>Ruang Kuliah 709</t>
-  </si>
-  <si>
-    <t>Ruang Kuliah 710</t>
-  </si>
-  <si>
-    <t>Ruang Kuliah 411</t>
-  </si>
-  <si>
-    <t>Ruang Kuliah 410</t>
-  </si>
-  <si>
-    <t>Ruang Kuliah 407</t>
-  </si>
-  <si>
-    <t>Ruang Ujian 911</t>
-  </si>
-  <si>
-    <t>Ruang Ujian 910</t>
-  </si>
-  <si>
-    <t>Ruang Ujian 908</t>
-  </si>
-  <si>
-    <t>Ruang Ujian 909</t>
-  </si>
-  <si>
-    <t>Ruang Ujian 907</t>
   </si>
 </sst>
 </file>
@@ -564,12 +507,12 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -925,21 +868,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="29" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
-      <c r="M1" s="27"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
+      <c r="I1" s="29"/>
+      <c r="J1" s="29"/>
+      <c r="K1" s="29"/>
+      <c r="L1" s="29"/>
+      <c r="M1" s="29"/>
     </row>
     <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1018,9 +961,7 @@
       <c r="L4" s="22">
         <v>2025</v>
       </c>
-      <c r="M4" s="28" t="s">
-        <v>88</v>
-      </c>
+      <c r="M4" s="27"/>
     </row>
     <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="17" t="s">
@@ -1057,9 +998,7 @@
       <c r="L5" s="22">
         <v>2025</v>
       </c>
-      <c r="M5" s="28" t="s">
-        <v>89</v>
-      </c>
+      <c r="M5" s="27"/>
     </row>
     <row r="6" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="9" t="s">
@@ -1096,9 +1035,7 @@
       <c r="L6" s="22">
         <v>2025</v>
       </c>
-      <c r="M6" s="28" t="s">
-        <v>90</v>
-      </c>
+      <c r="M6" s="27"/>
     </row>
     <row r="7" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="9" t="s">
@@ -1137,9 +1074,7 @@
       <c r="L7" s="22">
         <v>2025</v>
       </c>
-      <c r="M7" s="29" t="s">
-        <v>91</v>
-      </c>
+      <c r="M7" s="28"/>
     </row>
     <row r="8" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="9" t="s">
@@ -1178,9 +1113,7 @@
       <c r="L8" s="22">
         <v>2025</v>
       </c>
-      <c r="M8" s="29" t="s">
-        <v>92</v>
-      </c>
+      <c r="M8" s="28"/>
     </row>
     <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
@@ -1219,9 +1152,7 @@
       <c r="L9" s="22">
         <v>2025</v>
       </c>
-      <c r="M9" s="28" t="s">
-        <v>93</v>
-      </c>
+      <c r="M9" s="27"/>
     </row>
     <row r="10" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
@@ -1258,9 +1189,7 @@
       <c r="L10" s="22">
         <v>2025</v>
       </c>
-      <c r="M10" s="28" t="s">
-        <v>94</v>
-      </c>
+      <c r="M10" s="27"/>
     </row>
     <row r="11" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="17" t="s">
@@ -1297,9 +1226,7 @@
       <c r="L11" s="22">
         <v>2025</v>
       </c>
-      <c r="M11" s="28" t="s">
-        <v>95</v>
-      </c>
+      <c r="M11" s="27"/>
     </row>
     <row r="12" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="17" t="s">
@@ -1338,9 +1265,7 @@
       <c r="L12" s="22">
         <v>2025</v>
       </c>
-      <c r="M12" s="28" t="s">
-        <v>96</v>
-      </c>
+      <c r="M12" s="27"/>
     </row>
     <row r="13" spans="1:13" ht="31.8" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
@@ -1375,9 +1300,7 @@
       <c r="L13" s="22">
         <v>2025</v>
       </c>
-      <c r="M13" s="28" t="s">
-        <v>97</v>
-      </c>
+      <c r="M13" s="27"/>
     </row>
     <row r="14" spans="1:13" ht="31.8" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
@@ -1412,9 +1335,7 @@
       <c r="L14" s="22">
         <v>2025</v>
       </c>
-      <c r="M14" s="28" t="s">
-        <v>98</v>
-      </c>
+      <c r="M14" s="27"/>
     </row>
     <row r="15" spans="1:13" ht="31.8" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
@@ -1449,9 +1370,7 @@
       <c r="L15" s="22">
         <v>2025</v>
       </c>
-      <c r="M15" s="28" t="s">
-        <v>99</v>
-      </c>
+      <c r="M15" s="27"/>
     </row>
     <row r="16" spans="1:13" ht="31.8" x14ac:dyDescent="0.35">
       <c r="A16" s="17" t="s">
@@ -1488,9 +1407,7 @@
       <c r="L16" s="22">
         <v>2025</v>
       </c>
-      <c r="M16" s="28" t="s">
-        <v>100</v>
-      </c>
+      <c r="M16" s="27"/>
     </row>
     <row r="17" spans="1:13" ht="31.8" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
@@ -1527,9 +1444,7 @@
       <c r="L17" s="22">
         <v>2025</v>
       </c>
-      <c r="M17" s="28" t="s">
-        <v>101</v>
-      </c>
+      <c r="M17" s="27"/>
     </row>
     <row r="18" spans="1:13" ht="32.4" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A18" s="4" t="s">
@@ -1568,9 +1483,7 @@
       <c r="L18" s="22">
         <v>2025</v>
       </c>
-      <c r="M18" s="28" t="s">
-        <v>102</v>
-      </c>
+      <c r="M18" s="27"/>
     </row>
     <row r="19" spans="1:13" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
@@ -1607,9 +1520,7 @@
       <c r="L19" s="22">
         <v>2025</v>
       </c>
-      <c r="M19" s="29" t="s">
-        <v>103</v>
-      </c>
+      <c r="M19" s="28"/>
     </row>
     <row r="20" spans="1:13" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="s">
@@ -1648,9 +1559,7 @@
       <c r="L20" s="22">
         <v>2025</v>
       </c>
-      <c r="M20" s="29" t="s">
-        <v>104</v>
-      </c>
+      <c r="M20" s="28"/>
     </row>
     <row r="21" spans="1:13" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
@@ -1689,9 +1598,7 @@
       <c r="L21" s="22">
         <v>2025</v>
       </c>
-      <c r="M21" s="29" t="s">
-        <v>105</v>
-      </c>
+      <c r="M21" s="28"/>
     </row>
     <row r="22" spans="1:13" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="s">
@@ -1730,9 +1637,7 @@
       <c r="L22" s="22">
         <v>2025</v>
       </c>
-      <c r="M22" s="29" t="s">
-        <v>106</v>
-      </c>
+      <c r="M22" s="28"/>
     </row>
   </sheetData>
   <autoFilter ref="E1:E22" xr:uid="{95B44815-789E-44D5-B165-88C51CD1CA07}"/>
